--- a/data/nairobi/all_students.xlsx
+++ b/data/nairobi/all_students.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,25 +446,20 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Caleb Bett</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>English</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Kiswahili</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Kiswahili</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Science</t>
         </is>
@@ -486,17 +481,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>80</v>
+      </c>
       <c r="E2" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F2" t="n">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="G2" t="n">
-        <v>54</v>
-      </c>
-      <c r="H2" t="n">
         <v>92</v>
       </c>
     </row>
@@ -516,17 +510,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>74</v>
+      </c>
       <c r="E3" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="F3" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="G3" t="n">
-        <v>64</v>
-      </c>
-      <c r="H3" t="n">
         <v>54</v>
       </c>
     </row>
@@ -546,17 +539,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>94</v>
+      </c>
       <c r="E4" t="n">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="F4" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="G4" t="n">
-        <v>66</v>
-      </c>
-      <c r="H4" t="n">
         <v>84</v>
       </c>
     </row>
@@ -576,17 +568,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>45</v>
+      </c>
       <c r="E5" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F5" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="G5" t="n">
-        <v>52</v>
-      </c>
-      <c r="H5" t="n">
         <v>48</v>
       </c>
     </row>
@@ -606,17 +597,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>85</v>
+      </c>
       <c r="E6" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="F6" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G6" t="n">
-        <v>90</v>
-      </c>
-      <c r="H6" t="n">
         <v>88</v>
       </c>
     </row>
@@ -636,17 +626,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>68</v>
+      </c>
       <c r="E7" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F7" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G7" t="n">
-        <v>70</v>
-      </c>
-      <c r="H7" t="n">
         <v>65</v>
       </c>
     </row>
@@ -666,17 +655,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>55</v>
+      </c>
       <c r="E8" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F8" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="G8" t="n">
-        <v>61</v>
-      </c>
-      <c r="H8" t="n">
         <v>50</v>
       </c>
     </row>
@@ -696,17 +684,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>92</v>
+      </c>
       <c r="E9" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F9" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G9" t="n">
-        <v>85</v>
-      </c>
-      <c r="H9" t="n">
         <v>95</v>
       </c>
     </row>
@@ -726,17 +713,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>41</v>
+      </c>
       <c r="E10" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="F10" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G10" t="n">
-        <v>48</v>
-      </c>
-      <c r="H10" t="n">
         <v>38</v>
       </c>
     </row>
@@ -756,17 +742,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="n">
+        <v>79</v>
+      </c>
       <c r="E11" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F11" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G11" t="n">
-        <v>77</v>
-      </c>
-      <c r="H11" t="n">
         <v>83</v>
       </c>
     </row>
@@ -786,17 +771,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>63</v>
+      </c>
       <c r="E12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F12" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="G12" t="n">
-        <v>58</v>
-      </c>
-      <c r="H12" t="n">
         <v>72</v>
       </c>
     </row>
@@ -816,17 +800,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>87</v>
+      </c>
       <c r="E13" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F13" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="G13" t="n">
-        <v>89</v>
-      </c>
-      <c r="H13" t="n">
         <v>91</v>
       </c>
     </row>
@@ -846,17 +829,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>70</v>
+      </c>
       <c r="E14" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F14" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G14" t="n">
-        <v>73</v>
-      </c>
-      <c r="H14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -876,17 +858,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>58</v>
+      </c>
       <c r="E15" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F15" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G15" t="n">
-        <v>65</v>
-      </c>
-      <c r="H15" t="n">
         <v>59</v>
       </c>
     </row>
@@ -906,17 +887,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>76</v>
+      </c>
       <c r="E16" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F16" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="G16" t="n">
-        <v>82</v>
-      </c>
-      <c r="H16" t="n">
         <v>78</v>
       </c>
     </row>
@@ -936,17 +916,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>89</v>
+      </c>
       <c r="E17" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F17" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G17" t="n">
-        <v>87</v>
-      </c>
-      <c r="H17" t="n">
         <v>93</v>
       </c>
     </row>
@@ -966,17 +945,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="n">
+        <v>47</v>
+      </c>
       <c r="E18" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F18" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G18" t="n">
-        <v>50</v>
-      </c>
-      <c r="H18" t="n">
         <v>46</v>
       </c>
     </row>
@@ -996,17 +974,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>82</v>
+      </c>
       <c r="E19" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F19" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G19" t="n">
-        <v>85</v>
-      </c>
-      <c r="H19" t="n">
         <v>80</v>
       </c>
     </row>
@@ -1026,17 +1003,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="n">
+        <v>66</v>
+      </c>
       <c r="E20" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F20" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G20" t="n">
-        <v>64</v>
-      </c>
-      <c r="H20" t="n">
         <v>70</v>
       </c>
     </row>
@@ -1056,17 +1032,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="n">
+        <v>73</v>
+      </c>
       <c r="E21" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F21" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G21" t="n">
-        <v>71</v>
-      </c>
-      <c r="H21" t="n">
         <v>74</v>
       </c>
     </row>
@@ -1076,27 +1051,26 @@
           <t>S021</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Caleb Bett</t>
+        </is>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Caleb Bett</t>
-        </is>
+      <c r="D22" t="n">
+        <v>90</v>
       </c>
       <c r="E22" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F22" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G22" t="n">
-        <v>88</v>
-      </c>
-      <c r="H22" t="n">
         <v>87</v>
       </c>
     </row>
@@ -1116,17 +1090,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="n">
+        <v>52</v>
+      </c>
       <c r="E23" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F23" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G23" t="n">
-        <v>54</v>
-      </c>
-      <c r="H23" t="n">
         <v>61</v>
       </c>
     </row>
@@ -1146,17 +1119,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="n">
+        <v>81</v>
+      </c>
       <c r="E24" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F24" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G24" t="n">
-        <v>80</v>
-      </c>
-      <c r="H24" t="n">
         <v>85</v>
       </c>
     </row>
@@ -1176,17 +1148,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="n">
+        <v>60</v>
+      </c>
       <c r="E25" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F25" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G25" t="n">
-        <v>62</v>
-      </c>
-      <c r="H25" t="n">
         <v>58</v>
       </c>
     </row>
